--- a/data/trans_orig/P1421-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1421-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2007</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>20041</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42060</t>
+          <t>41759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59507</t>
+          <t>59211</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93523</t>
+          <t>93385</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85642</t>
+          <t>85069</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124324</t>
+          <t>125567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>989663</t>
+          <t>989964</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1011604</t>
+          <t>1011682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1221590</t>
+          <t>1221728</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1255606</t>
+          <t>1255902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2222511</t>
+          <t>2221268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2261193</t>
+          <t>2261766</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20756</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44284</t>
+          <t>44550</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72831</t>
+          <t>74357</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108654</t>
+          <t>112640</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101066</t>
+          <t>101888</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142558</t>
+          <t>144237</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1649129</t>
+          <t>1648863</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1672657</t>
+          <t>1672252</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1479019</t>
+          <t>1475033</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1514842</t>
+          <t>1513316</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3138528</t>
+          <t>3136849</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3180020</t>
+          <t>3179198</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10484</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27870</t>
+          <t>28256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19197</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40424</t>
+          <t>41231</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34943</t>
+          <t>34545</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61274</t>
+          <t>62080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>523538</t>
+          <t>523152</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540924</t>
+          <t>540051</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>435988</t>
+          <t>435181</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457215</t>
+          <t>457563</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>966546</t>
+          <t>965740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>992877</t>
+          <t>993275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62180</t>
+          <t>62800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97126</t>
+          <t>98230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>168059</t>
+          <t>170511</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>221885</t>
+          <t>224671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242222</t>
+          <t>243028</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>307169</t>
+          <t>305286</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3179417</t>
+          <t>3178313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3214363</t>
+          <t>3213743</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3157312</t>
+          <t>3154526</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3211138</t>
+          <t>3208686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6348572</t>
+          <t>6350455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6413519</t>
+          <t>6412713</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2012</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>25773</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63627</t>
+          <t>62880</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97486</t>
+          <t>98343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76301</t>
+          <t>77441</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116807</t>
+          <t>117867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>947407</t>
+          <t>948870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>965991</t>
+          <t>965415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1240311</t>
+          <t>1239454</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1274170</t>
+          <t>1274917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2195633</t>
+          <t>2194573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2236139</t>
+          <t>2234999</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15209</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34972</t>
+          <t>34898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68571</t>
+          <t>67919</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107748</t>
+          <t>105561</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89941</t>
+          <t>90438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133503</t>
+          <t>135002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1927955</t>
+          <t>1928029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1947718</t>
+          <t>1946798</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1646844</t>
+          <t>1649031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1686021</t>
+          <t>1686673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3584016</t>
+          <t>3582517</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3627578</t>
+          <t>3627081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>16452</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36808</t>
+          <t>37081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18648</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39203</t>
+          <t>39800</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>473435</t>
+          <t>474065</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>421823</t>
+          <t>421550</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>442063</t>
+          <t>442179</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>900610</t>
+          <t>900013</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>921165</t>
+          <t>921775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29471</t>
+          <t>30311</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55143</t>
+          <t>57087</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>161855</t>
+          <t>162943</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>217061</t>
+          <t>220587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>202755</t>
+          <t>201501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260765</t>
+          <t>263233</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3363608</t>
+          <t>3361664</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3389280</t>
+          <t>3388440</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3333959</t>
+          <t>3330433</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3389165</t>
+          <t>3388077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6709006</t>
+          <t>6706538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6767016</t>
+          <t>6768270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2016</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24995</t>
+          <t>24928</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55540</t>
+          <t>56102</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90673</t>
+          <t>92386</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69594</t>
+          <t>71269</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108447</t>
+          <t>111607</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>729352</t>
+          <t>729419</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>745203</t>
+          <t>745377</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>903987</t>
+          <t>902274</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>939120</t>
+          <t>938558</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1640560</t>
+          <t>1637400</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1679413</t>
+          <t>1677738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14205</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34625</t>
+          <t>36971</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77354</t>
+          <t>77245</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115319</t>
+          <t>115831</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98617</t>
+          <t>98059</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143254</t>
+          <t>143111</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2041760</t>
+          <t>2039414</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2062180</t>
+          <t>2061404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1872981</t>
+          <t>1872469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1910946</t>
+          <t>1911055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3921431</t>
+          <t>3921574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3966068</t>
+          <t>3966626</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16538</t>
+          <t>17609</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40142</t>
+          <t>40911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>27462</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52009</t>
+          <t>51084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>530348</t>
+          <t>529277</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542789</t>
+          <t>541976</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>508998</t>
+          <t>508229</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>530740</t>
+          <t>529859</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1044018</t>
+          <t>1044943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1069207</t>
+          <t>1068565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35685</t>
+          <t>35814</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64711</t>
+          <t>63838</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>168026</t>
+          <t>169272</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>223708</t>
+          <t>225838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212201</t>
+          <t>211255</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>273099</t>
+          <t>274256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3312907</t>
+          <t>3313780</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3341933</t>
+          <t>3341804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3308392</t>
+          <t>3306262</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3364074</t>
+          <t>3362828</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6636619</t>
+          <t>6635462</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6697517</t>
+          <t>6698463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2023</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15107</t>
+          <t>15777</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33991</t>
+          <t>32544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80828</t>
+          <t>80584</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111785</t>
+          <t>114217</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100338</t>
+          <t>101301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137693</t>
+          <t>140102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>478895</t>
+          <t>480342</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>497779</t>
+          <t>497109</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>640049</t>
+          <t>637617</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671006</t>
+          <t>671250</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1127026</t>
+          <t>1124617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1164381</t>
+          <t>1163418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70026</t>
+          <t>72325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131125</t>
+          <t>128426</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160468</t>
+          <t>155309</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>259978</t>
+          <t>263225</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257155</t>
+          <t>255786</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>376145</t>
+          <t>374130</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2158318</t>
+          <t>2161017</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2219417</t>
+          <t>2217118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1975073</t>
+          <t>1971826</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2074583</t>
+          <t>2079742</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4148349</t>
+          <t>4150364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4267339</t>
+          <t>4268708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38156</t>
+          <t>38038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54150</t>
+          <t>55198</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83333</t>
+          <t>84469</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78479</t>
+          <t>77658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113010</t>
+          <t>113175</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608467</t>
+          <t>608585</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629519</t>
+          <t>629867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>576970</t>
+          <t>575834</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>606153</t>
+          <t>605105</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1193917</t>
+          <t>1193752</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1228448</t>
+          <t>1229269</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116656</t>
+          <t>118824</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>179450</t>
+          <t>184047</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>315795</t>
+          <t>310377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>427009</t>
+          <t>426203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>464762</t>
+          <t>462286</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>595260</t>
+          <t>595804</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3269502</t>
+          <t>3264905</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3332296</t>
+          <t>3330128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3220178</t>
+          <t>3220984</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3331392</t>
+          <t>3336810</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6500880</t>
+          <t>6500336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6631378</t>
+          <t>6633854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1421-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1421-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20041</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41759</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59211</t>
+          <t>58190</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93385</t>
+          <t>91996</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85069</t>
+          <t>85589</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125567</t>
+          <t>125705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>989964</t>
+          <t>990815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1011682</t>
+          <t>1011063</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1221728</t>
+          <t>1223117</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1255902</t>
+          <t>1256923</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2221268</t>
+          <t>2221130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2261766</t>
+          <t>2261246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21161</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44550</t>
+          <t>44413</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74357</t>
+          <t>74265</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112640</t>
+          <t>111935</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101888</t>
+          <t>101741</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144237</t>
+          <t>147394</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1648863</t>
+          <t>1649000</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1672252</t>
+          <t>1672355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1475033</t>
+          <t>1475738</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1513316</t>
+          <t>1513408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3136849</t>
+          <t>3133692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3179198</t>
+          <t>3179345</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11357</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28256</t>
+          <t>26615</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18849</t>
+          <t>18224</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41231</t>
+          <t>39848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34545</t>
+          <t>34940</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62080</t>
+          <t>64025</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>523152</t>
+          <t>524793</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540051</t>
+          <t>540433</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>435181</t>
+          <t>436564</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457563</t>
+          <t>458188</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>965740</t>
+          <t>963795</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>993275</t>
+          <t>992880</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62800</t>
+          <t>63733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98230</t>
+          <t>98843</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>170511</t>
+          <t>168324</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>224671</t>
+          <t>222270</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>243028</t>
+          <t>241953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>305286</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3178313</t>
+          <t>3177700</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3213743</t>
+          <t>3212810</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3154526</t>
+          <t>3156927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3208686</t>
+          <t>3210873</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6350455</t>
+          <t>6351382</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6412713</t>
+          <t>6413788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25773</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62880</t>
+          <t>65013</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98343</t>
+          <t>100053</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77441</t>
+          <t>76484</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117867</t>
+          <t>117046</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>948870</t>
+          <t>949557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>965415</t>
+          <t>966171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1239454</t>
+          <t>1237744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1274917</t>
+          <t>1272784</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2194573</t>
+          <t>2195394</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2234999</t>
+          <t>2235956</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34898</t>
+          <t>33572</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67919</t>
+          <t>69172</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105561</t>
+          <t>107223</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90438</t>
+          <t>88458</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>135002</t>
+          <t>131007</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1928029</t>
+          <t>1929355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1946798</t>
+          <t>1948019</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1649031</t>
+          <t>1647369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1686673</t>
+          <t>1685420</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3582517</t>
+          <t>3586512</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3627081</t>
+          <t>3629061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>17405</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37081</t>
+          <t>37595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>18862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39800</t>
+          <t>40401</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>474065</t>
+          <t>474530</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>421550</t>
+          <t>421036</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>442179</t>
+          <t>441226</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>900013</t>
+          <t>899412</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>921775</t>
+          <t>920951</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30311</t>
+          <t>30073</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57087</t>
+          <t>55514</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162943</t>
+          <t>163757</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>220587</t>
+          <t>219156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>201501</t>
+          <t>201473</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>263233</t>
+          <t>259115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3361664</t>
+          <t>3363237</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3388440</t>
+          <t>3388678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3330433</t>
+          <t>3331864</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3388077</t>
+          <t>3387263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6706538</t>
+          <t>6710656</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6768270</t>
+          <t>6768298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24928</t>
+          <t>24625</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56102</t>
+          <t>56018</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92386</t>
+          <t>92023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71269</t>
+          <t>69914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111607</t>
+          <t>108012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>729419</t>
+          <t>729722</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>745377</t>
+          <t>744897</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>902274</t>
+          <t>902637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>938558</t>
+          <t>938642</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1637400</t>
+          <t>1640995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1677738</t>
+          <t>1679093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36971</t>
+          <t>34522</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77245</t>
+          <t>77308</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115831</t>
+          <t>115318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98059</t>
+          <t>95958</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143111</t>
+          <t>140962</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2039414</t>
+          <t>2041863</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2061404</t>
+          <t>2062214</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1872469</t>
+          <t>1872982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1911055</t>
+          <t>1910992</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3921574</t>
+          <t>3923723</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3966626</t>
+          <t>3968727</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17609</t>
+          <t>17285</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40911</t>
+          <t>40403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27462</t>
+          <t>27386</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51084</t>
+          <t>52713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>529277</t>
+          <t>529601</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541976</t>
+          <t>542589</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>508229</t>
+          <t>508737</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>529859</t>
+          <t>530404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1044943</t>
+          <t>1043314</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1068565</t>
+          <t>1068641</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>35157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63838</t>
+          <t>62484</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>169272</t>
+          <t>168292</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>225838</t>
+          <t>224728</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211255</t>
+          <t>211793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>274256</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3313780</t>
+          <t>3315134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3341804</t>
+          <t>3342461</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3306262</t>
+          <t>3307372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3362828</t>
+          <t>3363808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6635462</t>
+          <t>6636525</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6698463</t>
+          <t>6697925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22810</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32544</t>
+          <t>31295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>93892</t>
+          <t>96888</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80584</t>
+          <t>82606</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114217</t>
+          <t>112819</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>116702</t>
+          <t>119378</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101301</t>
+          <t>104085</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140102</t>
+          <t>136969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>490076</t>
+          <t>553956</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480342</t>
+          <t>545151</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>497109</t>
+          <t>561335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>657942</t>
+          <t>723059</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>637617</t>
+          <t>707128</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671250</t>
+          <t>737341</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1148017</t>
+          <t>1277015</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1124617</t>
+          <t>1259424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1163418</t>
+          <t>1292308</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>512886</t>
+          <t>576446</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512886</t>
+          <t>576446</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512886</t>
+          <t>576446</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751834</t>
+          <t>819947</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751834</t>
+          <t>819947</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751834</t>
+          <t>819947</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1264719</t>
+          <t>1396393</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1264719</t>
+          <t>1396393</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1264719</t>
+          <t>1396393</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>102468</t>
+          <t>107382</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72325</t>
+          <t>86809</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128426</t>
+          <t>134202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>223419</t>
+          <t>249159</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155309</t>
+          <t>224038</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>263225</t>
+          <t>276334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>325887</t>
+          <t>356541</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>255786</t>
+          <t>318737</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>374130</t>
+          <t>393297</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2186975</t>
+          <t>2120578</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2161017</t>
+          <t>2093758</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2217118</t>
+          <t>2141151</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2011632</t>
+          <t>1919384</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1971826</t>
+          <t>1892209</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2079742</t>
+          <t>1944505</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4198607</t>
+          <t>4039963</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4150364</t>
+          <t>4003207</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4268708</t>
+          <t>4077767</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289443</t>
+          <t>2227960</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289443</t>
+          <t>2227960</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289443</t>
+          <t>2227960</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235051</t>
+          <t>2168543</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235051</t>
+          <t>2168543</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235051</t>
+          <t>2168543</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524494</t>
+          <t>4396504</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524494</t>
+          <t>4396504</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524494</t>
+          <t>4396504</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26216</t>
+          <t>29194</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16756</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38038</t>
+          <t>42367</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>68224</t>
+          <t>75739</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55198</t>
+          <t>62522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84469</t>
+          <t>92752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>94440</t>
+          <t>104933</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77658</t>
+          <t>87132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113175</t>
+          <t>126421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>620407</t>
+          <t>682393</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608585</t>
+          <t>669220</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629867</t>
+          <t>692757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>592079</t>
+          <t>658456</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>575834</t>
+          <t>641443</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>605105</t>
+          <t>671673</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1212487</t>
+          <t>1340849</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1193752</t>
+          <t>1319361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1229269</t>
+          <t>1358650</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445782</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445782</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445782</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>151494</t>
+          <t>159066</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118824</t>
+          <t>134929</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>184047</t>
+          <t>188280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>385535</t>
+          <t>421786</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>310377</t>
+          <t>389668</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>426203</t>
+          <t>458281</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>537029</t>
+          <t>580852</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>462286</t>
+          <t>536294</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>595804</t>
+          <t>625187</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3297458</t>
+          <t>3356928</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3264905</t>
+          <t>3327714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3330128</t>
+          <t>3381065</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3261652</t>
+          <t>3300899</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3220984</t>
+          <t>3264404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3336810</t>
+          <t>3333017</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6559111</t>
+          <t>6657827</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6500336</t>
+          <t>6613492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6633854</t>
+          <t>6702385</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3448952</t>
+          <t>3515994</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3448952</t>
+          <t>3515994</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3448952</t>
+          <t>3515994</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3647187</t>
+          <t>3722685</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3647187</t>
+          <t>3722685</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3647187</t>
+          <t>3722685</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7096140</t>
+          <t>7238679</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7096140</t>
+          <t>7238679</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7096140</t>
+          <t>7238679</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
